--- a/docs/04_営業ツール/管理シート/営業管理（工務店ヒアリング・ペルソナ）.xlsx
+++ b/docs/04_営業ツール/管理シート/営業管理（工務店ヒアリング・ペルソナ）.xlsx
@@ -3172,7 +3172,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>「間取りの参考にしたい」→資料請求</t>
+          <t>「間取りの参考にしたい」→AI診断・会員登録</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
